--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136153124</v>
       </c>
       <c r="B2" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136153124</v>
       </c>
       <c r="B2" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136154324</v>
       </c>
       <c r="B3" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136153124</v>
       </c>
       <c r="B2" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136154324</v>
       </c>
       <c r="B3" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136153124</v>
       </c>
       <c r="B2" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136154324</v>
       </c>
       <c r="B3" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136153124</v>
       </c>
       <c r="B2" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136153124</v>
       </c>
       <c r="B2" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136154324</v>
       </c>
       <c r="B3" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136153124</v>
       </c>
       <c r="B2" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136153124</v>
       </c>
       <c r="B2" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136154324</v>
+        <v>136457569</v>
       </c>
       <c r="B3" t="n">
-        <v>58154</v>
+        <v>92512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tolseboda naturreservat, Tolseboda naturreservat, Bl</t>
+          <t>Tolseboda, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520865</v>
+        <v>520901</v>
       </c>
       <c r="R3" t="n">
-        <v>6243520</v>
+        <v>6243542</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,6 +877,108 @@
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136457569</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136154324</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tolseboda naturreservat, Tolseboda naturreservat, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>520865</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6243520</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hjortsberga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136154324</t>
         </is>
@@ -886,6 +988,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34168-2026 artfynd.xlsx
+++ b/artfynd/A 34168-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136153124</v>
       </c>
       <c r="B2" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136457569</v>
       </c>
       <c r="B3" t="n">
-        <v>92512</v>
+        <v>92513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
